--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -1465,10 +1465,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129505236</v>
+        <v>129504841</v>
       </c>
       <c r="B10" t="n">
-        <v>80178</v>
+        <v>80053</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,34 +1476,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590037</v>
+        <v>590084</v>
       </c>
       <c r="R10" t="n">
-        <v>6933025</v>
+        <v>6932834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129504841</v>
+        <v>129505236</v>
       </c>
       <c r="B11" t="n">
-        <v>80053</v>
+        <v>80178</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,34 +1573,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590084</v>
+        <v>590037</v>
       </c>
       <c r="R11" t="n">
-        <v>6932834</v>
+        <v>6933025</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -1368,45 +1368,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129505059</v>
+        <v>129505236</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590056</v>
+        <v>590037</v>
       </c>
       <c r="R9" t="n">
-        <v>6932848</v>
+        <v>6933025</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,32 +1465,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129504841</v>
+        <v>129505059</v>
       </c>
       <c r="B10" t="n">
-        <v>80053</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590084</v>
+        <v>590056</v>
       </c>
       <c r="R10" t="n">
-        <v>6932834</v>
+        <v>6932848</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129505236</v>
+        <v>129504841</v>
       </c>
       <c r="B11" t="n">
-        <v>80178</v>
+        <v>80053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,34 +1573,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590037</v>
+        <v>590084</v>
       </c>
       <c r="R11" t="n">
-        <v>6933025</v>
+        <v>6932834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -1368,45 +1368,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129505236</v>
+        <v>129505059</v>
       </c>
       <c r="B9" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590037</v>
+        <v>590056</v>
       </c>
       <c r="R9" t="n">
-        <v>6933025</v>
+        <v>6932848</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,32 +1465,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129505059</v>
+        <v>129504841</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>80053</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590056</v>
+        <v>590084</v>
       </c>
       <c r="R10" t="n">
-        <v>6932848</v>
+        <v>6932834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,32 +1562,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129504841</v>
+        <v>129504792</v>
       </c>
       <c r="B11" t="n">
-        <v>80053</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590084</v>
+        <v>590102</v>
       </c>
       <c r="R11" t="n">
-        <v>6932834</v>
+        <v>6932792</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,45 +1659,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129504792</v>
+        <v>129505236</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590102</v>
+        <v>590037</v>
       </c>
       <c r="R12" t="n">
-        <v>6932792</v>
+        <v>6933025</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -1562,45 +1562,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129504792</v>
+        <v>129505236</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>80178</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590102</v>
+        <v>590037</v>
       </c>
       <c r="R11" t="n">
-        <v>6932792</v>
+        <v>6933025</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,45 +1659,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129505236</v>
+        <v>129504792</v>
       </c>
       <c r="B12" t="n">
-        <v>80178</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590037</v>
+        <v>590102</v>
       </c>
       <c r="R12" t="n">
-        <v>6933025</v>
+        <v>6932792</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129505056</v>
       </c>
       <c r="B2" t="n">
-        <v>80053</v>
+        <v>80079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129505199</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129505066</v>
       </c>
       <c r="B4" t="n">
-        <v>80053</v>
+        <v>80079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129505106</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129505081</v>
       </c>
       <c r="B6" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>129505317</v>
       </c>
       <c r="B7" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>129505091</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,32 +1368,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129505059</v>
+        <v>129504841</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>80079</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1403,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590056</v>
+        <v>590084</v>
       </c>
       <c r="R9" t="n">
-        <v>6932848</v>
+        <v>6932834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,32 +1465,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129504841</v>
+        <v>129504792</v>
       </c>
       <c r="B10" t="n">
-        <v>80053</v>
+        <v>80175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590084</v>
+        <v>590102</v>
       </c>
       <c r="R10" t="n">
-        <v>6932834</v>
+        <v>6932792</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,45 +1562,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129505236</v>
+        <v>129505059</v>
       </c>
       <c r="B11" t="n">
-        <v>80178</v>
+        <v>80175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590037</v>
+        <v>590056</v>
       </c>
       <c r="R11" t="n">
-        <v>6933025</v>
+        <v>6932848</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,45 +1659,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129504792</v>
+        <v>129505236</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80204</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590102</v>
+        <v>590037</v>
       </c>
       <c r="R12" t="n">
-        <v>6932792</v>
+        <v>6933025</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -1368,10 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129504841</v>
+        <v>129505236</v>
       </c>
       <c r="B9" t="n">
-        <v>80079</v>
+        <v>80204</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,34 +1379,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590084</v>
+        <v>590037</v>
       </c>
       <c r="R9" t="n">
-        <v>6932834</v>
+        <v>6933025</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,32 +1465,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129504792</v>
+        <v>129504841</v>
       </c>
       <c r="B10" t="n">
-        <v>80175</v>
+        <v>80079</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590102</v>
+        <v>590084</v>
       </c>
       <c r="R10" t="n">
-        <v>6932792</v>
+        <v>6932834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129505059</v>
+        <v>129504792</v>
       </c>
       <c r="B11" t="n">
         <v>80175</v>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590056</v>
+        <v>590102</v>
       </c>
       <c r="R11" t="n">
-        <v>6932848</v>
+        <v>6932792</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,45 +1659,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129505236</v>
+        <v>129505059</v>
       </c>
       <c r="B12" t="n">
-        <v>80204</v>
+        <v>80175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590037</v>
+        <v>590056</v>
       </c>
       <c r="R12" t="n">
-        <v>6933025</v>
+        <v>6932848</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129505056</v>
       </c>
       <c r="B2" t="n">
-        <v>80079</v>
+        <v>80084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129505199</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129505066</v>
       </c>
       <c r="B4" t="n">
-        <v>80079</v>
+        <v>80084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129505106</v>
       </c>
       <c r="B5" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,54 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129505081</v>
+        <v>129505317</v>
       </c>
       <c r="B6" t="n">
-        <v>57834</v>
+        <v>80180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590076</v>
+        <v>590050</v>
       </c>
       <c r="R6" t="n">
-        <v>6932863</v>
+        <v>6933090</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129505317</v>
+        <v>129505091</v>
       </c>
       <c r="B7" t="n">
-        <v>80175</v>
+        <v>57732</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1180,34 +1171,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590050</v>
+        <v>590076</v>
       </c>
       <c r="R7" t="n">
-        <v>6933090</v>
+        <v>6932863</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129505091</v>
+        <v>129505059</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>80180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1277,39 +1273,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590076</v>
+        <v>590056</v>
       </c>
       <c r="R8" t="n">
-        <v>6932863</v>
+        <v>6932848</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129505236</v>
+        <v>129504841</v>
       </c>
       <c r="B9" t="n">
-        <v>80204</v>
+        <v>80084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,34 +1370,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590037</v>
+        <v>590084</v>
       </c>
       <c r="R9" t="n">
-        <v>6933025</v>
+        <v>6932834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129504841</v>
+        <v>129505236</v>
       </c>
       <c r="B10" t="n">
-        <v>80079</v>
+        <v>80209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1476,34 +1467,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590084</v>
+        <v>590037</v>
       </c>
       <c r="R10" t="n">
-        <v>6932834</v>
+        <v>6933025</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1565,7 +1556,7 @@
         <v>129504792</v>
       </c>
       <c r="B11" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,45 +1650,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129505059</v>
+        <v>129505081</v>
       </c>
       <c r="B12" t="n">
-        <v>80175</v>
+        <v>57839</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590056</v>
+        <v>590076</v>
       </c>
       <c r="R12" t="n">
-        <v>6932848</v>
+        <v>6932863</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129505056</v>
       </c>
       <c r="B2" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129505199</v>
       </c>
       <c r="B3" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129505066</v>
       </c>
       <c r="B4" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129505106</v>
       </c>
       <c r="B5" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129505317</v>
       </c>
       <c r="B6" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>129505091</v>
       </c>
       <c r="B7" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129505059</v>
       </c>
       <c r="B8" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>129504841</v>
       </c>
       <c r="B9" t="n">
-        <v>80084</v>
+        <v>80085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129505236</v>
       </c>
       <c r="B10" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>129504792</v>
       </c>
       <c r="B11" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>129505081</v>
       </c>
       <c r="B12" t="n">
-        <v>57839</v>
+        <v>57840</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129505056</v>
       </c>
       <c r="B2" t="n">
-        <v>80085</v>
+        <v>80090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,45 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129505199</v>
+        <v>129505066</v>
       </c>
       <c r="B3" t="n">
-        <v>80181</v>
+        <v>80090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590041</v>
+        <v>590076</v>
       </c>
       <c r="R3" t="n">
-        <v>6933010</v>
+        <v>6932863</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,45 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129505066</v>
+        <v>129505199</v>
       </c>
       <c r="B4" t="n">
-        <v>80085</v>
+        <v>80186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590076</v>
+        <v>590041</v>
       </c>
       <c r="R4" t="n">
-        <v>6932863</v>
+        <v>6933010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>129505106</v>
       </c>
       <c r="B5" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129505317</v>
       </c>
       <c r="B6" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129505059</v>
+        <v>129504841</v>
       </c>
       <c r="B8" t="n">
-        <v>80181</v>
+        <v>80090</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590056</v>
+        <v>590084</v>
       </c>
       <c r="R8" t="n">
-        <v>6932848</v>
+        <v>6932834</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129504841</v>
+        <v>129505236</v>
       </c>
       <c r="B9" t="n">
-        <v>80085</v>
+        <v>80215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590084</v>
+        <v>590037</v>
       </c>
       <c r="R9" t="n">
-        <v>6932834</v>
+        <v>6933025</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,45 +1456,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129505236</v>
+        <v>129504792</v>
       </c>
       <c r="B10" t="n">
-        <v>80210</v>
+        <v>80186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590037</v>
+        <v>590102</v>
       </c>
       <c r="R10" t="n">
-        <v>6933025</v>
+        <v>6932792</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129504792</v>
+        <v>129505059</v>
       </c>
       <c r="B11" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590102</v>
+        <v>590056</v>
       </c>
       <c r="R11" t="n">
-        <v>6932792</v>
+        <v>6932848</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -1359,45 +1359,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129505236</v>
+        <v>129505059</v>
       </c>
       <c r="B9" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590037</v>
+        <v>590056</v>
       </c>
       <c r="R9" t="n">
-        <v>6933025</v>
+        <v>6932848</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,45 +1456,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129504792</v>
+        <v>129505236</v>
       </c>
       <c r="B10" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590102</v>
+        <v>590037</v>
       </c>
       <c r="R10" t="n">
-        <v>6932792</v>
+        <v>6933025</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129505059</v>
+        <v>129504792</v>
       </c>
       <c r="B11" t="n">
         <v>80186</v>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590056</v>
+        <v>590102</v>
       </c>
       <c r="R11" t="n">
-        <v>6932848</v>
+        <v>6932792</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -772,45 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129505066</v>
+        <v>129505199</v>
       </c>
       <c r="B3" t="n">
-        <v>80090</v>
+        <v>80186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590076</v>
+        <v>590041</v>
       </c>
       <c r="R3" t="n">
-        <v>6932863</v>
+        <v>6933010</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,45 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129505199</v>
+        <v>129505066</v>
       </c>
       <c r="B4" t="n">
-        <v>80186</v>
+        <v>80090</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590041</v>
+        <v>590076</v>
       </c>
       <c r="R4" t="n">
-        <v>6933010</v>
+        <v>6932863</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129504841</v>
+        <v>129505059</v>
       </c>
       <c r="B8" t="n">
-        <v>80090</v>
+        <v>80186</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590084</v>
+        <v>590056</v>
       </c>
       <c r="R8" t="n">
-        <v>6932834</v>
+        <v>6932848</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129505059</v>
+        <v>129504841</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>80090</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590056</v>
+        <v>590084</v>
       </c>
       <c r="R9" t="n">
-        <v>6932848</v>
+        <v>6932834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -1262,45 +1262,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129505059</v>
+        <v>129505236</v>
       </c>
       <c r="B8" t="n">
-        <v>80186</v>
+        <v>80215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590056</v>
+        <v>590037</v>
       </c>
       <c r="R8" t="n">
-        <v>6932848</v>
+        <v>6933025</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129504841</v>
+        <v>129505059</v>
       </c>
       <c r="B9" t="n">
-        <v>80090</v>
+        <v>80186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590084</v>
+        <v>590056</v>
       </c>
       <c r="R9" t="n">
-        <v>6932834</v>
+        <v>6932848</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129505236</v>
+        <v>129504841</v>
       </c>
       <c r="B10" t="n">
-        <v>80215</v>
+        <v>80090</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,34 +1467,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590037</v>
+        <v>590084</v>
       </c>
       <c r="R10" t="n">
-        <v>6933025</v>
+        <v>6932834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -1262,45 +1262,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129505236</v>
+        <v>129505059</v>
       </c>
       <c r="B8" t="n">
-        <v>80215</v>
+        <v>80186</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590037</v>
+        <v>590056</v>
       </c>
       <c r="R8" t="n">
-        <v>6933025</v>
+        <v>6932848</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129505059</v>
+        <v>129504841</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>80090</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590056</v>
+        <v>590084</v>
       </c>
       <c r="R9" t="n">
-        <v>6932848</v>
+        <v>6932834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129504841</v>
+        <v>129505236</v>
       </c>
       <c r="B10" t="n">
-        <v>80090</v>
+        <v>80215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,34 +1467,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590084</v>
+        <v>590037</v>
       </c>
       <c r="R10" t="n">
-        <v>6932834</v>
+        <v>6933025</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -1653,7 +1653,7 @@
         <v>129505081</v>
       </c>
       <c r="B12" t="n">
-        <v>57840</v>
+        <v>57841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129505056</v>
+        <v>129504841</v>
       </c>
       <c r="B2" t="n">
-        <v>80090</v>
+        <v>80336</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590056</v>
+        <v>590084</v>
       </c>
       <c r="R2" t="n">
-        <v>6932848</v>
+        <v>6932834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129505199</v>
+        <v>129505056</v>
       </c>
       <c r="B3" t="n">
-        <v>80186</v>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590041</v>
+        <v>590056</v>
       </c>
       <c r="R3" t="n">
-        <v>6933010</v>
+        <v>6932848</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129505066</v>
       </c>
       <c r="B4" t="n">
-        <v>80090</v>
+        <v>80336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129505106</v>
+        <v>129504792</v>
       </c>
       <c r="B5" t="n">
-        <v>80186</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590079</v>
+        <v>590102</v>
       </c>
       <c r="R5" t="n">
-        <v>6932890</v>
+        <v>6932792</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129505317</v>
+        <v>129505059</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Näverbäcken, Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590050</v>
+        <v>590056</v>
       </c>
       <c r="R6" t="n">
-        <v>6933090</v>
+        <v>6932848</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129505091</v>
+        <v>129505106</v>
       </c>
       <c r="B7" t="n">
-        <v>57733</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,39 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590076</v>
+        <v>590079</v>
       </c>
       <c r="R7" t="n">
-        <v>6932863</v>
+        <v>6932890</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129505059</v>
+        <v>129505199</v>
       </c>
       <c r="B8" t="n">
-        <v>80186</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1293,14 +1288,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590056</v>
+        <v>590041</v>
       </c>
       <c r="R8" t="n">
-        <v>6932848</v>
+        <v>6933010</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,45 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129504841</v>
+        <v>129505317</v>
       </c>
       <c r="B9" t="n">
-        <v>80090</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Näverbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590084</v>
+        <v>590050</v>
       </c>
       <c r="R9" t="n">
-        <v>6932834</v>
+        <v>6933090</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,7 +1454,7 @@
         <v>129505236</v>
       </c>
       <c r="B10" t="n">
-        <v>80215</v>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,45 +1548,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129504792</v>
+        <v>129505091</v>
       </c>
       <c r="B11" t="n">
-        <v>80186</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590102</v>
+        <v>590076</v>
       </c>
       <c r="R11" t="n">
-        <v>6932792</v>
+        <v>6932863</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,11 +1653,11 @@
         <v>129505081</v>
       </c>
       <c r="B12" t="n">
-        <v>57844</v>
+        <v>58057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">

--- a/artfynd/A 49642-2025 artfynd.xlsx
+++ b/artfynd/A 49642-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129504841</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505056</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505066</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129504792</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505059</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505106</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505199</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505317</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505236</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505091</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1753,8 +1808,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505081</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>